--- a/kiln-shelves/plan.xlsx
+++ b/kiln-shelves/plan.xlsx
@@ -984,7 +984,7 @@
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Thickness not in title; set to Advancer standard 5/16" - confirm.</t>
+          <t>Thickness not in the old title; Advancer lists its multi-sided shelves at 5/16".</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1062,7 +1062,7 @@
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Thickness not in title; set to Advancer standard 5/16" - confirm. Vendor part no. (AKS-ADV2020F10S-1) duplicates the 20" full shelf's.</t>
+          <t>Thickness not in the old title; Advancer lists its multi-sided shelves at 5/16". Vendor part no. (AKS-ADV2020F10S-1) duplicates the 20" full shelf's.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1140,7 +1140,7 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Thickness not in title; set to Advancer standard 5/16" - confirm.</t>
+          <t>Thickness not in the old title; Advancer lists its multi-sided shelves at 5/16".</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Thickness not in title; set to Advancer standard 5/16" - confirm.</t>
+          <t>Thickness not in the old title; Advancer lists its multi-sided shelves at 5/16".</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Thickness not in title; set to Advancer standard 5/16" - confirm.</t>
+          <t>Thickness not in the old title; Advancer lists its multi-sided shelves at 5/16".</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1709,156 +1709,148 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Advancer Kiln Shelf 13 x26 x 5/16" Nitride Bonded Silicon Carbide Rectangle</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Advancer Silicon Carbide Kiln Shelf - 13" x 26" Rectangle, 5/16" Thick</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>13" x 26"</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Rectangle</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>5/16"</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Advancer Kiln Shelves | Sheffield Pottery | Nitride Bonded Silicon Carbide</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>Advancer Kiln Shelf 13" x 26" x 5/16" Rectangle | Sheffield Pottery</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>Description opens with "12 x28"; fix the description.</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>Advancer</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>SSFADV1326</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>advancer-kiln-shelf-13-x26-x-5-16-silicon-carbide-ssfadv1326</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>gid://shopify/Product/8316337586498</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>https://www.sheffield-pottery.com/products/advancer-kiln-shelf-13-x26-x-5-16-silicon-carbide-ssfadv1326</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Advancer Kiln Shelf 14 x 28 x 5/16" Nitride Bonded Silicon Carbide Rectangle</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Advancer Silicon Carbide Kiln Shelf - 14" x 28" Rectangle, 5/16" Thick</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>14" x 28"</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Rectangle</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>5/16"</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Advancer Kiln Shelves | Sheffield Pottery | Nitride Bonded Silicon Carbide</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>Advancer Kiln Shelf 14" x 28" x 5/16" Rectangle | Sheffield Pottery</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>Description opens with "11 x 22"; fix the description.</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>Advancer</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>SSFADV1428</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>advancer-kiln-shelf-14-x28-x-5-16-silicon-carbide-ssfadv1428</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>gid://shopify/Product/8316337848642</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>https://www.sheffield-pottery.com/products/advancer-kiln-shelf-14-x28-x-5-16-silicon-carbide-ssfadv1428</t>
         </is>
@@ -2797,12 +2789,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Cedar Heights CoreLite Semi-Hollow Kiln Shelf - 16" x 15" Full 8-Sided, 5/8" Thick</t>
+          <t>Cedar Heights CoreLite Semi-Hollow Kiln Shelf - 15" x 16" Full 8-Sided, 5/8" Thick</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>16" Diameter</t>
+          <t>15" Diameter</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2822,7 +2814,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>CoreLite Semi-Hollow Kiln Shelf 16" x 15" x 5/8" Full 8-Sided</t>
+          <t>CoreLite Semi-Hollow Kiln Shelf 15" x 16" x 5/8" Full 8-Sided</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -2832,7 +2824,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>Octagon listed as 16" x 15" (corner-to-corner x flat-to-flat?); filed under 16" Diameter - confirm.</t>
+          <t>Old title said 16" x 15"; sold as a 15" octagon, so filed under 15" Diameter.</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -4777,156 +4769,148 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>26 1/2" X 1" Half Round High Alumina Kiln Shelf</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>Spectrum High Alumina Kiln Shelf - 26 1/2" Half Round, 1" Thick</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>26 1/2" Diameter</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>Half Round</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>1"</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G57" s="4" t="inlineStr">
         <is>
           <t>27 1/2" x 3/4" HALF ROUND HIGH ALUMINA KILN SHELF</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H57" s="4" t="inlineStr">
         <is>
           <t>Spectrum High Alumina Kiln Shelf 26 1/2" x 1" Half Round</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr"/>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>Old SEO title said 27 1/2" and meta description says 28 1/2"; fix the meta description too.</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
+      <c r="I57" s="5" t="inlineStr"/>
+      <c r="J57" s="5" t="inlineStr"/>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
         <is>
           <t>Spectrum Kiln Shelves</t>
         </is>
       </c>
-      <c r="M57" s="2" t="inlineStr">
+      <c r="M57" s="4" t="inlineStr">
         <is>
           <t>SPHA261</t>
         </is>
       </c>
-      <c r="N57" s="2" t="inlineStr">
+      <c r="N57" s="4" t="inlineStr">
         <is>
           <t>26-1-2-x-1-half-round-high-alumina-kiln-shelf</t>
         </is>
       </c>
-      <c r="O57" s="2" t="inlineStr">
+      <c r="O57" s="4" t="inlineStr">
         <is>
           <t>gid://shopify/Product/15042839904627</t>
         </is>
       </c>
-      <c r="P57" s="2" t="inlineStr">
+      <c r="P57" s="4" t="inlineStr">
         <is>
           <t>https://www.sheffield-pottery.com/products/26-1-2-x-1-half-round-high-alumina-kiln-shelf</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>26 1/2" X 3/4" Half Round High Alumina Kiln Shelf</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>Spectrum High Alumina Kiln Shelf - 26 1/2" Half Round, 3/4" Thick</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>26 1/2" Diameter</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>Half Round</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>3/4"</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" s="4" t="inlineStr">
         <is>
           <t>27 1/2" x 3/4" HALF ROUND HIGH ALUMINA KILN SHELF</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H58" s="4" t="inlineStr">
         <is>
           <t>Spectrum High Alumina Kiln Shelf 26 1/2" x 3/4" Half Round</t>
         </is>
       </c>
-      <c r="I58" s="3" t="inlineStr"/>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>Old SEO title said 27 1/2" and meta description says 28 1/2"; fix the meta description too.</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="I58" s="5" t="inlineStr"/>
+      <c r="J58" s="5" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
         <is>
           <t>Spectrum Kiln Shelves</t>
         </is>
       </c>
-      <c r="M58" s="2" t="inlineStr">
+      <c r="M58" s="4" t="inlineStr">
         <is>
           <t>SPHA01</t>
         </is>
       </c>
-      <c r="N58" s="2" t="inlineStr">
+      <c r="N58" s="4" t="inlineStr">
         <is>
           <t>kiln-shelf-spha01</t>
         </is>
       </c>
-      <c r="O58" s="2" t="inlineStr">
+      <c r="O58" s="4" t="inlineStr">
         <is>
           <t>gid://shopify/Product/8316330737986</t>
         </is>
       </c>
-      <c r="P58" s="2" t="inlineStr">
+      <c r="P58" s="4" t="inlineStr">
         <is>
           <t>https://www.sheffield-pottery.com/products/kiln-shelf-spha01</t>
         </is>
@@ -5307,78 +5291,74 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>26" X 13" X 3/4" Rectangle High Alumina Kiln Shelf</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>Spectrum High Alumina Kiln Shelf - 13" x 26" Rectangle, 3/4" Thick</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>13" x 26"</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>Rectangle</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>3/4"</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>26" x 13" x 3/4" RECTANGLE HIGH ALUMI</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>Spectrum High Alumina Kiln Shelf 13" x 26" x 3/4" Rectangle</t>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr"/>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>Description says 26" x 13" x 1"; title and SKU say 3/4" (the 1" version is archived). Fix the description.</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="I64" s="5" t="inlineStr"/>
+      <c r="J64" s="5" t="inlineStr"/>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
         <is>
           <t>Spectrum Kiln Shelves</t>
         </is>
       </c>
-      <c r="M64" s="2" t="inlineStr">
+      <c r="M64" s="4" t="inlineStr">
         <is>
           <t>SPHA09</t>
         </is>
       </c>
-      <c r="N64" s="2" t="inlineStr">
+      <c r="N64" s="4" t="inlineStr">
         <is>
           <t>kiln-shelf-spha09</t>
         </is>
       </c>
-      <c r="O64" s="2" t="inlineStr">
+      <c r="O64" s="4" t="inlineStr">
         <is>
           <t>gid://shopify/Product/8316331786562</t>
         </is>
       </c>
-      <c r="P64" s="2" t="inlineStr">
+      <c r="P64" s="4" t="inlineStr">
         <is>
           <t>https://www.sheffield-pottery.com/products/kiln-shelf-spha09</t>
         </is>
